--- a/deliverables/uiss/X14_UISS_Batch_ASNSubmit.xlsx
+++ b/deliverables/uiss/X14_UISS_Batch_ASNSubmit.xlsx
@@ -37246,7 +37246,7 @@
       </c>
       <c r="D9" s="948" t="inlineStr">
         <is>
-          <t>The log follows the existing NSP log (same table and columns); the Submit ID is the key to find the run.</t>
+          <t>The log follows the existing Supplier System log (same table and columns); the Submit ID is the key to find the run.</t>
         </is>
       </c>
       <c r="E9" s="941" t="n"/>
@@ -37694,7 +37694,7 @@
       </c>
       <c r="D13" s="948" t="inlineStr">
         <is>
-          <t>The submit process (Submit ID, batch call, log) follows the existing ASN submit of NSP.</t>
+          <t>The submit process (Submit ID, batch call, log) follows the existing ASN submit of Supplier System.</t>
         </is>
       </c>
       <c r="E13" s="941" t="n"/>
@@ -51241,7 +51241,7 @@
       <c r="D43" s="941" t="n"/>
       <c r="E43" s="948" t="inlineStr">
         <is>
-          <t>Transaction table - Existing ASN header table of NSP; the crossdock ASN is saved here after submit. Only the fields used are listed; physical names follow the existing table.</t>
+          <t>Transaction table - Existing ASN header table of Supplier System; the crossdock ASN is saved here after submit. Only the fields used are listed; physical names follow the existing table.</t>
         </is>
       </c>
       <c r="F43" s="941" t="n"/>
@@ -53291,7 +53291,7 @@
       <c r="D61" s="1024" t="n"/>
       <c r="E61" s="1058" t="inlineStr">
         <is>
-          <t>Transaction table - Existing ASN part / case table of NSP. Only the fields used are listed; physical names follow the existing table.</t>
+          <t>Transaction table - Existing ASN part / case table of Supplier System. Only the fields used are listed; physical names follow the existing table.</t>
         </is>
       </c>
       <c r="F61" s="1024" t="n"/>

--- a/deliverables/uiss/X14_UISS_Batch_ASNSubmit.xlsx
+++ b/deliverables/uiss/X14_UISS_Batch_ASNSubmit.xlsx
@@ -37246,7 +37246,7 @@
       </c>
       <c r="D9" s="948" t="inlineStr">
         <is>
-          <t>The log follows the existing Supplier System log (same table and columns); the Submit ID is the key to find the run.</t>
+          <t>The log follows the existing NSP log (same table and columns); the Submit ID is the key to find the run.</t>
         </is>
       </c>
       <c r="E9" s="941" t="n"/>
@@ -37694,7 +37694,7 @@
       </c>
       <c r="D13" s="948" t="inlineStr">
         <is>
-          <t>The submit process (Submit ID, batch call, log) follows the existing ASN submit of Supplier System.</t>
+          <t>The submit process (Submit ID, batch call, log) follows the existing ASN submit of NSP.</t>
         </is>
       </c>
       <c r="E13" s="941" t="n"/>
@@ -51241,7 +51241,7 @@
       <c r="D43" s="941" t="n"/>
       <c r="E43" s="948" t="inlineStr">
         <is>
-          <t>Transaction table - Existing ASN header table of Supplier System; the crossdock ASN is saved here after submit. Only the fields used are listed; physical names follow the existing table.</t>
+          <t>Transaction table - Existing ASN header table of NSP; the crossdock ASN is saved here after submit. Only the fields used are listed; physical names follow the existing table.</t>
         </is>
       </c>
       <c r="F43" s="941" t="n"/>
@@ -53291,7 +53291,7 @@
       <c r="D61" s="1024" t="n"/>
       <c r="E61" s="1058" t="inlineStr">
         <is>
-          <t>Transaction table - Existing ASN part / case table of Supplier System. Only the fields used are listed; physical names follow the existing table.</t>
+          <t>Transaction table - Existing ASN part / case table of NSP. Only the fields used are listed; physical names follow the existing table.</t>
         </is>
       </c>
       <c r="F61" s="1024" t="n"/>
